--- a/src/test/resources/testdata/RegistrationData.xlsx
+++ b/src/test/resources/testdata/RegistrationData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\eclipse-workspace\SeleniumTestNGFramework\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B4CE49-6940-444C-A32A-E8102954E8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C208C153-04F3-4D71-9A06-2FE407CAEB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CEA3D30B-A4F6-4F3A-A61A-8F9A636D2ECA}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
+    <sheet name="Execution Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="98">
   <si>
     <t>Name</t>
   </si>
@@ -123,58 +124,211 @@
     <t>Pune</t>
   </si>
   <si>
-    <t>ORD691163</t>
-  </si>
-  <si>
-    <t>ORD838800</t>
-  </si>
-  <si>
-    <t>ORD445475</t>
-  </si>
-  <si>
-    <t>ORD410259</t>
-  </si>
-  <si>
-    <t>ORD192215</t>
-  </si>
-  <si>
-    <t>ORD222879</t>
-  </si>
-  <si>
-    <t>ORD339574</t>
-  </si>
-  <si>
-    <t>ORD206539</t>
-  </si>
-  <si>
-    <t>ORD616469</t>
-  </si>
-  <si>
-    <t>ORD724366</t>
-  </si>
-  <si>
-    <t>ORD462451</t>
-  </si>
-  <si>
-    <t>ORD860519</t>
-  </si>
-  <si>
-    <t>ORD903028</t>
-  </si>
-  <si>
-    <t>ORD772325</t>
-  </si>
-  <si>
-    <t>ORD728240</t>
-  </si>
-  <si>
-    <t>ORD571396</t>
-  </si>
-  <si>
-    <t>ORD700496</t>
-  </si>
-  <si>
-    <t>ORD214661</t>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>LOCAL</t>
+  </si>
+  <si>
+    <t>TC005</t>
+  </si>
+  <si>
+    <t>Jithi</t>
+  </si>
+  <si>
+    <t>Jithi@gmail.com</t>
+  </si>
+  <si>
+    <t>TC006</t>
+  </si>
+  <si>
+    <t>Ramu</t>
+  </si>
+  <si>
+    <t>Ramu@gmail.com</t>
+  </si>
+  <si>
+    <t>TC007</t>
+  </si>
+  <si>
+    <t>TC009</t>
+  </si>
+  <si>
+    <t>TC010</t>
+  </si>
+  <si>
+    <t>TC011</t>
+  </si>
+  <si>
+    <t>Raju</t>
+  </si>
+  <si>
+    <t>Rani</t>
+  </si>
+  <si>
+    <t>Hyma</t>
+  </si>
+  <si>
+    <t>Chandu</t>
+  </si>
+  <si>
+    <t>raju@gmail.com</t>
+  </si>
+  <si>
+    <t>rani@gmail.com</t>
+  </si>
+  <si>
+    <t>hyma@gmail.com</t>
+  </si>
+  <si>
+    <t>chandu@gmail.com</t>
+  </si>
+  <si>
+    <t>Bengalore</t>
+  </si>
+  <si>
+    <t>TC008</t>
+  </si>
+  <si>
+    <t>ORD311772</t>
+  </si>
+  <si>
+    <t>ORD623987</t>
+  </si>
+  <si>
+    <t>ORD682116</t>
+  </si>
+  <si>
+    <t>ORD989742</t>
+  </si>
+  <si>
+    <t>ORD815039</t>
+  </si>
+  <si>
+    <t>ORD982419</t>
+  </si>
+  <si>
+    <t>ORD272801</t>
+  </si>
+  <si>
+    <t>ORD107353</t>
+  </si>
+  <si>
+    <t>ORD515607</t>
+  </si>
+  <si>
+    <t>AUTOMATION EXECUTION DASHBOARD</t>
+  </si>
+  <si>
+    <t>Execution Information</t>
+  </si>
+  <si>
+    <t>Browser :</t>
+  </si>
+  <si>
+    <t>CHROME</t>
+  </si>
+  <si>
+    <t>Environment :</t>
+  </si>
+  <si>
+    <t>Execution Mode :</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Driver Mode :</t>
+  </si>
+  <si>
+    <t>Start Time :</t>
+  </si>
+  <si>
+    <t>28-Jul-2026 11:21:11 am</t>
+  </si>
+  <si>
+    <t>End Time :</t>
+  </si>
+  <si>
+    <t>28-Jul-2026 11:22:37 am</t>
+  </si>
+  <si>
+    <t>Execution Duration :</t>
+  </si>
+  <si>
+    <t>00:01:25</t>
+  </si>
+  <si>
+    <t>Execution Statistics</t>
+  </si>
+  <si>
+    <t>Total Tests :</t>
+  </si>
+  <si>
+    <t>Executed Tests :</t>
+  </si>
+  <si>
+    <t>Passed Tests :</t>
+  </si>
+  <si>
+    <t>Failed Tests :</t>
+  </si>
+  <si>
+    <t>Skipped Tests :</t>
+  </si>
+  <si>
+    <t>Pass Percentage :</t>
+  </si>
+  <si>
+    <t>100.00 %</t>
+  </si>
+  <si>
+    <t>Fail Percentage :</t>
+  </si>
+  <si>
+    <t>0.00 %</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ORD185423</t>
+  </si>
+  <si>
+    <t>28-Jul-2026 11:55:06 am</t>
+  </si>
+  <si>
+    <t>28-Jul-2026 11:55:15 am</t>
+  </si>
+  <si>
+    <t>00:00:09</t>
+  </si>
+  <si>
+    <t>28-Jul-2026 12:08:04 pm</t>
+  </si>
+  <si>
+    <t>28-Jul-2026 12:08:05 pm</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>ORD878783</t>
+  </si>
+  <si>
+    <t>ORD427062</t>
+  </si>
+  <si>
+    <t>ORD891807</t>
+  </si>
+  <si>
+    <t>28-Jul-2026 12:26:23 pm</t>
+  </si>
+  <si>
+    <t>28-Jul-2026 12:26:45 pm</t>
+  </si>
+  <si>
+    <t>00:00:22</t>
   </si>
 </sst>
 </file>
@@ -182,7 +336,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,16 +352,170 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="16.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="16.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="16.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="18"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="18"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -215,17 +523,98 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -541,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1401C1A3-B549-472E-8462-9AF5D93F8B65}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" customWidth="true" width="23.453125"/>
@@ -607,7 +996,7 @@
         <v>24</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>46</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -636,7 +1025,7 @@
         <v>24</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>44</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -644,7 +1033,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>6</v>
@@ -657,6 +1046,15 @@
       </c>
       <c r="F4" t="s" s="0">
         <v>12</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -664,7 +1062,7 @@
         <v>25</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>26</v>
@@ -685,7 +1083,201 @@
         <v>24</v>
       </c>
       <c r="I5" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="0">
+        <v>7654321567</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="0">
+        <v>7654287654</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="0">
+        <v>7653134561</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>45</v>
+      </c>
+      <c r="E9" s="0">
+        <v>7654289651</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="0">
+        <v>6526698751</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="0">
+        <v>6426789651</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="0">
+        <v>2323984812</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -694,7 +1286,162 @@
     <hyperlink ref="D3" r:id="rId2" xr:uid="{B3D31A15-4766-45AA-A6BE-289C522C4412}"/>
     <hyperlink ref="D2" r:id="rId3" xr:uid="{104BD369-FB3D-4F32-9515-42BCC8248F34}"/>
     <hyperlink ref="D5" r:id="rId4" xr:uid="{DF89B5F8-C959-4DE8-AFC5-C7FADC6867A8}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{DC80E246-671B-46F8-8C43-EE62B39F61CF}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{59FE1EB4-E002-4318-AA97-50A1022D164E}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{96029F06-4DB7-49AB-8884-B749E630F6E9}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{AD523ED6-E733-4EB4-BEE8-F5A2501BCF5B}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{E699D884-3D2C-4D8D-979A-3F30C2D7757D}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{A39FB45B-0954-4A44-8BAC-B4CA66534711}"/>
+    <hyperlink ref="D12" r:id="rId11" xr:uid="{122A10ED-C838-4AEE-A4EB-B937D5E56F74}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="35.15625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="46.875"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30.0" customHeight="true">
+      <c r="A1" t="s" s="33">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="24.0" customHeight="true">
+      <c r="A3" t="s" s="34">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" ht="22.0" customHeight="true">
+      <c r="A4" t="s" s="35">
+        <v>62</v>
+      </c>
+      <c r="B4" t="s" s="36">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" ht="22.0" customHeight="true">
+      <c r="A5" t="s" s="35">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s" s="36">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="22.0" customHeight="true">
+      <c r="A6" t="s" s="35">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s" s="36">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" ht="22.0" customHeight="true">
+      <c r="A7" t="s" s="35">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s" s="36">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="22.0" customHeight="true">
+      <c r="A8" t="s" s="35">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s" s="36">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" ht="22.0" customHeight="true">
+      <c r="A9" t="s" s="35">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s" s="36">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" ht="22.0" customHeight="true">
+      <c r="A10" t="s" s="35">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s" s="36">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="24.0" customHeight="true">
+      <c r="A12" t="s" s="37">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" ht="22.0" customHeight="true">
+      <c r="A13" t="s" s="38">
+        <v>75</v>
+      </c>
+      <c r="B13" t="n" s="39">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="14" ht="22.0" customHeight="true">
+      <c r="A14" t="s" s="38">
+        <v>76</v>
+      </c>
+      <c r="B14" t="n" s="39">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="15" ht="22.0" customHeight="true">
+      <c r="A15" t="s" s="38">
+        <v>77</v>
+      </c>
+      <c r="B15" t="n" s="40">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="16" ht="22.0" customHeight="true">
+      <c r="A16" t="s" s="38">
+        <v>78</v>
+      </c>
+      <c r="B16" t="n" s="41">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="17" ht="22.0" customHeight="true">
+      <c r="A17" t="s" s="38">
+        <v>79</v>
+      </c>
+      <c r="B17" t="n" s="42">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18" ht="22.0" customHeight="true">
+      <c r="A18" t="s" s="38">
+        <v>80</v>
+      </c>
+      <c r="B18" t="s" s="40">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" ht="22.0" customHeight="true">
+      <c r="A19" t="s" s="38">
+        <v>82</v>
+      </c>
+      <c r="B19" t="s" s="41">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testdata/RegistrationData.xlsx
+++ b/src/test/resources/testdata/RegistrationData.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="103">
   <si>
     <t>Name</t>
   </si>
@@ -329,6 +329,21 @@
   </si>
   <si>
     <t>00:00:22</t>
+  </si>
+  <si>
+    <t>02-Aug-2026 02:47:48 pm</t>
+  </si>
+  <si>
+    <t>02-Aug-2026 02:52:09 pm</t>
+  </si>
+  <si>
+    <t>00:04:21</t>
+  </si>
+  <si>
+    <t>66.67 %</t>
+  </si>
+  <si>
+    <t>33.33 %</t>
   </si>
 </sst>
 </file>
@@ -336,7 +351,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,6 +392,32 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="16.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -561,7 +602,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -611,6 +652,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="true" applyAlignment="true" applyFill="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyBorder="true" applyFill="true"/>
@@ -1308,132 +1361,132 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="true">
-      <c r="A1" t="s" s="33">
+      <c r="A1" t="s" s="43">
         <v>60</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3" ht="24.0" customHeight="true">
-      <c r="A3" t="s" s="34">
+      <c r="A3" t="s" s="44">
         <v>61</v>
       </c>
     </row>
     <row r="4" ht="22.0" customHeight="true">
-      <c r="A4" t="s" s="35">
+      <c r="A4" t="s" s="45">
         <v>62</v>
       </c>
-      <c r="B4" t="s" s="36">
+      <c r="B4" t="s" s="46">
         <v>63</v>
       </c>
     </row>
     <row r="5" ht="22.0" customHeight="true">
-      <c r="A5" t="s" s="35">
+      <c r="A5" t="s" s="45">
         <v>64</v>
       </c>
-      <c r="B5" t="s" s="36">
+      <c r="B5" t="s" s="46">
         <v>29</v>
       </c>
     </row>
     <row r="6" ht="22.0" customHeight="true">
-      <c r="A6" t="s" s="35">
+      <c r="A6" t="s" s="45">
         <v>65</v>
       </c>
-      <c r="B6" t="s" s="36">
+      <c r="B6" t="s" s="46">
         <v>66</v>
       </c>
     </row>
     <row r="7" ht="22.0" customHeight="true">
-      <c r="A7" t="s" s="35">
+      <c r="A7" t="s" s="45">
         <v>67</v>
       </c>
-      <c r="B7" t="s" s="36">
+      <c r="B7" t="s" s="46">
         <v>30</v>
       </c>
     </row>
     <row r="8" ht="22.0" customHeight="true">
-      <c r="A8" t="s" s="35">
+      <c r="A8" t="s" s="45">
         <v>68</v>
       </c>
-      <c r="B8" t="s" s="36">
-        <v>95</v>
+      <c r="B8" t="s" s="46">
+        <v>98</v>
       </c>
     </row>
     <row r="9" ht="22.0" customHeight="true">
-      <c r="A9" t="s" s="35">
+      <c r="A9" t="s" s="45">
         <v>70</v>
       </c>
-      <c r="B9" t="s" s="36">
-        <v>96</v>
+      <c r="B9" t="s" s="46">
+        <v>99</v>
       </c>
     </row>
     <row r="10" ht="22.0" customHeight="true">
-      <c r="A10" t="s" s="35">
+      <c r="A10" t="s" s="45">
         <v>72</v>
       </c>
-      <c r="B10" t="s" s="36">
-        <v>97</v>
+      <c r="B10" t="s" s="46">
+        <v>100</v>
       </c>
     </row>
     <row r="11"/>
     <row r="12" ht="24.0" customHeight="true">
-      <c r="A12" t="s" s="37">
+      <c r="A12" t="s" s="47">
         <v>74</v>
       </c>
     </row>
     <row r="13" ht="22.0" customHeight="true">
-      <c r="A13" t="s" s="38">
+      <c r="A13" t="s" s="48">
         <v>75</v>
       </c>
-      <c r="B13" t="n" s="39">
-        <v>3.0</v>
+      <c r="B13" t="n" s="49">
+        <v>6.0</v>
       </c>
     </row>
     <row r="14" ht="22.0" customHeight="true">
-      <c r="A14" t="s" s="38">
+      <c r="A14" t="s" s="48">
         <v>76</v>
       </c>
-      <c r="B14" t="n" s="39">
-        <v>3.0</v>
+      <c r="B14" t="n" s="49">
+        <v>6.0</v>
       </c>
     </row>
     <row r="15" ht="22.0" customHeight="true">
-      <c r="A15" t="s" s="38">
+      <c r="A15" t="s" s="48">
         <v>77</v>
       </c>
-      <c r="B15" t="n" s="40">
-        <v>3.0</v>
+      <c r="B15" t="n" s="50">
+        <v>4.0</v>
       </c>
     </row>
     <row r="16" ht="22.0" customHeight="true">
-      <c r="A16" t="s" s="38">
+      <c r="A16" t="s" s="48">
         <v>78</v>
       </c>
-      <c r="B16" t="n" s="41">
+      <c r="B16" t="n" s="51">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17" ht="22.0" customHeight="true">
+      <c r="A17" t="s" s="48">
+        <v>79</v>
+      </c>
+      <c r="B17" t="n" s="52">
         <v>0.0</v>
       </c>
     </row>
-    <row r="17" ht="22.0" customHeight="true">
-      <c r="A17" t="s" s="38">
-        <v>79</v>
-      </c>
-      <c r="B17" t="n" s="42">
-        <v>0.0</v>
-      </c>
-    </row>
     <row r="18" ht="22.0" customHeight="true">
-      <c r="A18" t="s" s="38">
+      <c r="A18" t="s" s="48">
         <v>80</v>
       </c>
-      <c r="B18" t="s" s="40">
-        <v>81</v>
+      <c r="B18" t="s" s="50">
+        <v>101</v>
       </c>
     </row>
     <row r="19" ht="22.0" customHeight="true">
-      <c r="A19" t="s" s="38">
+      <c r="A19" t="s" s="48">
         <v>82</v>
       </c>
-      <c r="B19" t="s" s="41">
-        <v>83</v>
+      <c r="B19" t="s" s="51">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
